--- a/inventories/baseline/lci-Salar-de-Arizaro.xlsx
+++ b/inventories/baseline/lci-Salar-de-Arizaro.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leidenuniv1-my.sharepoint.com/personal/istrateir_vuw_leidenuniv_nl/Documents/Research/lithium-brine-prospective-LCA/inventories/baseline/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_98E69100DD3FB811212A3760A50424BB744A068E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5DB3519-B7C3-438C-BB49-9FAFB894E216}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Salar de Arizaro" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -229,8 +235,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,13 +282,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -320,7 +334,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -354,6 +368,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -388,9 +403,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -563,11 +579,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F276"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="66.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -575,7 +594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -583,7 +602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -591,7 +610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -599,7 +618,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -607,7 +626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -615,7 +634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -623,7 +642,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -631,12 +650,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -656,12 +675,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.00025</v>
+        <v>2.5000000000000001E-4</v>
       </c>
       <c r="D12" t="s">
         <v>16</v>
@@ -673,12 +692,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
       <c r="B13">
-        <v>0.00125</v>
+        <v>1.25E-3</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
@@ -690,7 +709,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -707,12 +726,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
       <c r="B15">
-        <v>0.007206</v>
+        <v>7.2059999999999997E-3</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -724,7 +743,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>2</v>
       </c>
@@ -732,7 +751,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -740,7 +759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -748,7 +767,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -756,7 +775,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -764,7 +783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -772,7 +791,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -780,12 +799,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -805,7 +824,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -822,7 +841,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -839,7 +858,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -856,12 +875,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>15</v>
       </c>
       <c r="B29">
-        <v>0.0001111111111111111</v>
+        <v>1.111111111111111E-4</v>
       </c>
       <c r="D29" t="s">
         <v>16</v>
@@ -873,7 +892,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -890,7 +909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -907,12 +926,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
       <c r="B32">
-        <v>1.111111111111111</v>
+        <v>1.1111111111111109</v>
       </c>
       <c r="C32" t="s">
         <v>1</v>
@@ -924,12 +943,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
       <c r="B33">
-        <v>-0.0001111111111111111</v>
+        <v>-1.111111111111111E-4</v>
       </c>
       <c r="C33" t="s">
         <v>1</v>
@@ -941,7 +960,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>2</v>
       </c>
@@ -949,7 +968,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -957,7 +976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -965,7 +984,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -973,7 +992,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>7</v>
       </c>
@@ -981,7 +1000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -989,7 +1008,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -997,12 +1016,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -1022,7 +1041,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -1039,12 +1058,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>3</v>
       </c>
       <c r="B45">
-        <v>0.07444691366490365</v>
+        <v>7.4446913664903649E-2</v>
       </c>
       <c r="C45" t="s">
         <v>1</v>
@@ -1056,12 +1075,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>36</v>
       </c>
       <c r="B46">
-        <v>1.328598171454929</v>
+        <v>1.3285981714549291</v>
       </c>
       <c r="C46" t="s">
         <v>1</v>
@@ -1073,7 +1092,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>37</v>
       </c>
@@ -1090,12 +1109,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>39</v>
       </c>
       <c r="B48">
-        <v>0.0006333333333333333</v>
+        <v>6.333333333333333E-4</v>
       </c>
       <c r="C48" t="s">
         <v>40</v>
@@ -1107,12 +1126,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>22</v>
       </c>
       <c r="B49">
-        <v>0.001720222535539387</v>
+        <v>1.7202225355393869E-3</v>
       </c>
       <c r="C49" t="s">
         <v>23</v>
@@ -1124,12 +1143,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>41</v>
       </c>
       <c r="B50">
-        <v>-0.0003</v>
+        <v>-2.9999999999999997E-4</v>
       </c>
       <c r="C50" t="s">
         <v>40</v>
@@ -1141,7 +1160,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>2</v>
       </c>
@@ -1149,7 +1168,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -1157,7 +1176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -1165,7 +1184,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1173,7 +1192,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -1181,7 +1200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>8</v>
       </c>
@@ -1189,7 +1208,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>10</v>
       </c>
@@ -1197,12 +1216,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>13</v>
       </c>
@@ -1222,7 +1241,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>43</v>
       </c>
@@ -1239,7 +1258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>42</v>
       </c>
@@ -1256,7 +1275,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>44</v>
       </c>
@@ -1273,12 +1292,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>37</v>
       </c>
       <c r="B64">
-        <v>0.918754015176356</v>
+        <v>0.91875401517635602</v>
       </c>
       <c r="C64" t="s">
         <v>1</v>
@@ -1290,7 +1309,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>2</v>
       </c>
@@ -1298,7 +1317,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>4</v>
       </c>
@@ -1306,7 +1325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -1314,7 +1333,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -1322,7 +1341,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -1330,7 +1349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>8</v>
       </c>
@@ -1338,7 +1357,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>10</v>
       </c>
@@ -1346,12 +1365,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>13</v>
       </c>
@@ -1371,7 +1390,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>45</v>
       </c>
@@ -1388,12 +1407,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>3</v>
       </c>
       <c r="B76">
-        <v>0.02340491080726006</v>
+        <v>2.3404910807260058E-2</v>
       </c>
       <c r="C76" t="s">
         <v>1</v>
@@ -1405,12 +1424,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>26</v>
       </c>
       <c r="B77">
-        <v>0.970743861490925</v>
+        <v>0.97074386149092495</v>
       </c>
       <c r="C77" t="s">
         <v>1</v>
@@ -1422,12 +1441,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>37</v>
       </c>
       <c r="B78">
-        <v>0.2708077227499978</v>
+        <v>0.27080772274999781</v>
       </c>
       <c r="C78" t="s">
         <v>1</v>
@@ -1439,12 +1458,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>46</v>
       </c>
       <c r="B79">
-        <v>0.005851227701815015</v>
+        <v>5.8512277018150146E-3</v>
       </c>
       <c r="C79" t="s">
         <v>47</v>
@@ -1456,7 +1475,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>2</v>
       </c>
@@ -1464,7 +1483,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -1472,7 +1491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>5</v>
       </c>
@@ -1480,7 +1499,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>6</v>
       </c>
@@ -1488,7 +1507,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>7</v>
       </c>
@@ -1496,7 +1515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>8</v>
       </c>
@@ -1504,7 +1523,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>10</v>
       </c>
@@ -1512,12 +1531,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>13</v>
       </c>
@@ -1537,7 +1556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>48</v>
       </c>
@@ -1554,12 +1573,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>3</v>
       </c>
       <c r="B91">
-        <v>0.06944103186205777</v>
+        <v>6.9441031862057773E-2</v>
       </c>
       <c r="C91" t="s">
         <v>1</v>
@@ -1571,12 +1590,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>49</v>
       </c>
       <c r="B92">
-        <v>0.9131987101724277</v>
+        <v>0.91319871017242771</v>
       </c>
       <c r="C92" t="s">
         <v>1</v>
@@ -1588,12 +1607,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>37</v>
       </c>
       <c r="B93">
-        <v>0.1751894090885998</v>
+        <v>0.17518940908859981</v>
       </c>
       <c r="C93" t="s">
         <v>1</v>
@@ -1605,12 +1624,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>46</v>
       </c>
       <c r="B94">
-        <v>0.01736025796551444</v>
+        <v>1.736025796551444E-2</v>
       </c>
       <c r="C94" t="s">
         <v>47</v>
@@ -1622,7 +1641,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>2</v>
       </c>
@@ -1630,7 +1649,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>4</v>
       </c>
@@ -1638,7 +1657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>5</v>
       </c>
@@ -1646,7 +1665,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>6</v>
       </c>
@@ -1654,7 +1673,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>7</v>
       </c>
@@ -1662,7 +1681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -1670,7 +1689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>10</v>
       </c>
@@ -1678,12 +1697,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>13</v>
       </c>
@@ -1703,7 +1722,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>36</v>
       </c>
@@ -1720,12 +1739,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>48</v>
       </c>
       <c r="B106">
-        <v>0.9855854590029834</v>
+        <v>0.98558545900298344</v>
       </c>
       <c r="C106" t="s">
         <v>1</v>
@@ -1737,12 +1756,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>50</v>
       </c>
       <c r="B107">
-        <v>0.01441454099701651</v>
+        <v>1.4414540997016509E-2</v>
       </c>
       <c r="C107" t="s">
         <v>40</v>
@@ -1754,7 +1773,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>2</v>
       </c>
@@ -1762,7 +1781,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>4</v>
       </c>
@@ -1770,7 +1789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -1778,7 +1797,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>6</v>
       </c>
@@ -1786,7 +1805,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>7</v>
       </c>
@@ -1794,7 +1813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>8</v>
       </c>
@@ -1802,7 +1821,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>10</v>
       </c>
@@ -1810,12 +1829,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>13</v>
       </c>
@@ -1835,7 +1854,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>51</v>
       </c>
@@ -1852,12 +1871,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>42</v>
       </c>
       <c r="B119">
-        <v>7.716400289835759</v>
+        <v>7.7164002898357591</v>
       </c>
       <c r="C119" t="s">
         <v>1</v>
@@ -1869,12 +1888,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>22</v>
       </c>
       <c r="B120">
-        <v>0.008222393751464333</v>
+        <v>8.2223937514643332E-3</v>
       </c>
       <c r="C120" t="s">
         <v>23</v>
@@ -1886,12 +1905,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>34</v>
       </c>
       <c r="B121">
-        <v>-0.006716400289835759</v>
+        <v>-6.7164002898357587E-3</v>
       </c>
       <c r="C121" t="s">
         <v>1</v>
@@ -1903,7 +1922,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>2</v>
       </c>
@@ -1911,7 +1930,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>4</v>
       </c>
@@ -1919,7 +1938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>5</v>
       </c>
@@ -1927,7 +1946,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>6</v>
       </c>
@@ -1935,7 +1954,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>7</v>
       </c>
@@ -1943,7 +1962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>8</v>
       </c>
@@ -1951,7 +1970,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>10</v>
       </c>
@@ -1959,12 +1978,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>13</v>
       </c>
@@ -1984,7 +2003,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>52</v>
       </c>
@@ -2001,12 +2020,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>45</v>
       </c>
       <c r="B133">
-        <v>212.4652359691973</v>
+        <v>212.46523596919729</v>
       </c>
       <c r="C133" t="s">
         <v>1</v>
@@ -2018,12 +2037,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>22</v>
       </c>
       <c r="B134">
-        <v>0.2263973825901283</v>
+        <v>0.22639738259012829</v>
       </c>
       <c r="C134" t="s">
         <v>23</v>
@@ -2035,12 +2054,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>34</v>
       </c>
       <c r="B135">
-        <v>-0.02114652359691974</v>
+        <v>-2.114652359691974E-2</v>
       </c>
       <c r="C135" t="s">
         <v>1</v>
@@ -2052,7 +2071,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>2</v>
       </c>
@@ -2060,7 +2079,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>4</v>
       </c>
@@ -2068,7 +2087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>5</v>
       </c>
@@ -2076,7 +2095,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>6</v>
       </c>
@@ -2084,7 +2103,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>7</v>
       </c>
@@ -2092,7 +2111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>8</v>
       </c>
@@ -2100,7 +2119,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>10</v>
       </c>
@@ -2108,12 +2127,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>13</v>
       </c>
@@ -2133,7 +2152,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>53</v>
       </c>
@@ -2150,7 +2169,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>54</v>
       </c>
@@ -2167,12 +2186,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>22</v>
       </c>
       <c r="B148">
-        <v>0.002486338797814208</v>
+        <v>2.4863387978142082E-3</v>
       </c>
       <c r="C148" t="s">
         <v>23</v>
@@ -2184,12 +2203,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>34</v>
       </c>
       <c r="B149">
-        <v>-0.001333333333333333</v>
+        <v>-1.3333333333333331E-3</v>
       </c>
       <c r="C149" t="s">
         <v>1</v>
@@ -2201,7 +2220,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>2</v>
       </c>
@@ -2209,7 +2228,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>4</v>
       </c>
@@ -2217,7 +2236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>5</v>
       </c>
@@ -2225,7 +2244,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>6</v>
       </c>
@@ -2233,7 +2252,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>7</v>
       </c>
@@ -2241,7 +2260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>8</v>
       </c>
@@ -2249,7 +2268,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>10</v>
       </c>
@@ -2257,12 +2276,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>13</v>
       </c>
@@ -2282,7 +2301,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>44</v>
       </c>
@@ -2299,12 +2318,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>3</v>
       </c>
       <c r="B161">
-        <v>0.8460236886632826</v>
+        <v>0.84602368866328259</v>
       </c>
       <c r="C161" t="s">
         <v>1</v>
@@ -2316,12 +2335,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>55</v>
       </c>
       <c r="B162">
-        <v>0.1539763113367174</v>
+        <v>0.15397631133671741</v>
       </c>
       <c r="C162" t="s">
         <v>1</v>
@@ -2333,7 +2352,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>22</v>
       </c>
@@ -2350,7 +2369,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>2</v>
       </c>
@@ -2358,7 +2377,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>4</v>
       </c>
@@ -2366,7 +2385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>5</v>
       </c>
@@ -2374,7 +2393,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>6</v>
       </c>
@@ -2382,7 +2401,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>7</v>
       </c>
@@ -2390,7 +2409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>8</v>
       </c>
@@ -2398,7 +2417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>10</v>
       </c>
@@ -2406,12 +2425,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>13</v>
       </c>
@@ -2431,12 +2450,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>56</v>
       </c>
       <c r="B174">
-        <v>0.000260655737704918</v>
+        <v>2.6065573770491798E-4</v>
       </c>
       <c r="D174" t="s">
         <v>11</v>
@@ -2448,7 +2467,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>27</v>
       </c>
@@ -2465,7 +2484,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>30</v>
       </c>
@@ -2482,7 +2501,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>32</v>
       </c>
@@ -2499,7 +2518,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>15</v>
       </c>
@@ -2516,7 +2535,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>49</v>
       </c>
@@ -2533,7 +2552,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>3</v>
       </c>
@@ -2550,7 +2569,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>57</v>
       </c>
@@ -2567,12 +2586,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>22</v>
       </c>
       <c r="B182">
-        <v>0.0001656513157894737</v>
+        <v>1.656513157894737E-4</v>
       </c>
       <c r="C182" t="s">
         <v>23</v>
@@ -2584,7 +2603,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>59</v>
       </c>
@@ -2601,12 +2620,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>60</v>
       </c>
       <c r="B184">
-        <v>9.000000000000001E-05</v>
+        <v>9.0000000000000006E-5</v>
       </c>
       <c r="C184" t="s">
         <v>40</v>
@@ -2618,7 +2637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>61</v>
       </c>
@@ -2635,12 +2654,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>34</v>
       </c>
       <c r="B186">
-        <v>-5E-05</v>
+        <v>-5.0000000000000002E-5</v>
       </c>
       <c r="C186" t="s">
         <v>1</v>
@@ -2652,7 +2671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>2</v>
       </c>
@@ -2660,7 +2679,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>4</v>
       </c>
@@ -2668,7 +2687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>5</v>
       </c>
@@ -2676,7 +2695,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>6</v>
       </c>
@@ -2684,7 +2703,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="192" spans="1:6">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>7</v>
       </c>
@@ -2692,7 +2711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:6">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>8</v>
       </c>
@@ -2700,7 +2719,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:6">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>10</v>
       </c>
@@ -2708,12 +2727,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:6">
+    <row r="195" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="196" spans="1:6">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>13</v>
       </c>
@@ -2733,12 +2752,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="197" spans="1:6">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>62</v>
       </c>
       <c r="B197">
-        <v>-0.00023</v>
+        <v>-2.3000000000000001E-4</v>
       </c>
       <c r="D197" t="s">
         <v>11</v>
@@ -2750,12 +2769,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="198" spans="1:6">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>43</v>
       </c>
       <c r="B198">
-        <v>-0.00162</v>
+        <v>-1.6199999999999999E-3</v>
       </c>
       <c r="D198" t="s">
         <v>38</v>
@@ -2767,12 +2786,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="199" spans="1:6">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>64</v>
       </c>
       <c r="B199">
-        <v>-7.000000000000001E-05</v>
+        <v>-7.0000000000000007E-5</v>
       </c>
       <c r="D199" t="s">
         <v>11</v>
@@ -2784,7 +2803,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="200" spans="1:6">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>33</v>
       </c>
@@ -2801,12 +2820,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="201" spans="1:6">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>3</v>
       </c>
       <c r="B201">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
       <c r="C201" t="s">
         <v>1</v>
@@ -2818,7 +2837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="202" spans="1:6">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>65</v>
       </c>
@@ -2835,12 +2854,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="203" spans="1:6">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>22</v>
       </c>
       <c r="B203">
-        <v>0.0008199999999999999</v>
+        <v>8.1999999999999987E-4</v>
       </c>
       <c r="C203" t="s">
         <v>23</v>
@@ -2852,12 +2871,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="204" spans="1:6">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>50</v>
       </c>
       <c r="B204">
-        <v>0.00024</v>
+        <v>2.4000000000000001E-4</v>
       </c>
       <c r="C204" t="s">
         <v>40</v>
@@ -2869,12 +2888,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="205" spans="1:6">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>66</v>
       </c>
       <c r="B205">
-        <v>0.00012</v>
+        <v>1.2E-4</v>
       </c>
       <c r="C205" t="s">
         <v>47</v>
@@ -2886,7 +2905,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="207" spans="1:6">
+    <row r="207" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>2</v>
       </c>
@@ -2894,7 +2913,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="208" spans="1:6">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>4</v>
       </c>
@@ -2902,7 +2921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:6">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>5</v>
       </c>
@@ -2910,7 +2929,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="210" spans="1:6">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>6</v>
       </c>
@@ -2918,7 +2937,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="211" spans="1:6">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>7</v>
       </c>
@@ -2926,7 +2945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:6">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>8</v>
       </c>
@@ -2934,7 +2953,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="213" spans="1:6">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>10</v>
       </c>
@@ -2942,12 +2961,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="214" spans="1:6">
+    <row r="214" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="215" spans="1:6">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>13</v>
       </c>
@@ -2967,7 +2986,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="216" spans="1:6">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>43</v>
       </c>
@@ -2984,7 +3003,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="217" spans="1:6">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>67</v>
       </c>
@@ -3001,7 +3020,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="218" spans="1:6">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>53</v>
       </c>
@@ -3018,12 +3037,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="219" spans="1:6">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>37</v>
       </c>
       <c r="B219">
-        <v>0.3529411764705883</v>
+        <v>0.35294117647058831</v>
       </c>
       <c r="C219" t="s">
         <v>1</v>
@@ -3035,7 +3054,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="220" spans="1:6">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>22</v>
       </c>
@@ -3052,7 +3071,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="222" spans="1:6">
+    <row r="222" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>2</v>
       </c>
@@ -3060,7 +3079,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="223" spans="1:6">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>4</v>
       </c>
@@ -3068,7 +3087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:6">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>5</v>
       </c>
@@ -3076,7 +3095,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="225" spans="1:6">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>6</v>
       </c>
@@ -3084,7 +3103,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="226" spans="1:6">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>7</v>
       </c>
@@ -3092,7 +3111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:6">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>8</v>
       </c>
@@ -3100,7 +3119,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="228" spans="1:6">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>10</v>
       </c>
@@ -3108,12 +3127,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="229" spans="1:6">
+    <row r="229" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="230" spans="1:6">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>13</v>
       </c>
@@ -3133,7 +3152,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="231" spans="1:6">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>65</v>
       </c>
@@ -3150,12 +3169,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="232" spans="1:6">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>35</v>
       </c>
       <c r="B232">
-        <v>2.277</v>
+        <v>2.2770000000000001</v>
       </c>
       <c r="C232" t="s">
         <v>1</v>
@@ -3167,7 +3186,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="233" spans="1:6">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>37</v>
       </c>
@@ -3184,12 +3203,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="234" spans="1:6">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>22</v>
       </c>
       <c r="B234">
-        <v>0.00333219512195122</v>
+        <v>3.33219512195122E-3</v>
       </c>
       <c r="C234" t="s">
         <v>23</v>
@@ -3201,12 +3220,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="235" spans="1:6">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>68</v>
       </c>
       <c r="B235">
-        <v>0.0125</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="C235" t="s">
         <v>40</v>
@@ -3218,7 +3237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="237" spans="1:6">
+    <row r="237" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>2</v>
       </c>
@@ -3226,7 +3245,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="238" spans="1:6">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>4</v>
       </c>
@@ -3234,7 +3253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:6">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>5</v>
       </c>
@@ -3242,7 +3261,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="240" spans="1:6">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>6</v>
       </c>
@@ -3250,7 +3269,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="241" spans="1:6">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>7</v>
       </c>
@@ -3258,7 +3277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:6">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>8</v>
       </c>
@@ -3266,7 +3285,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="243" spans="1:6">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>10</v>
       </c>
@@ -3274,12 +3293,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="244" spans="1:6">
+    <row r="244" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="245" spans="1:6">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>13</v>
       </c>
@@ -3299,7 +3318,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="246" spans="1:6">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>54</v>
       </c>
@@ -3316,7 +3335,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="247" spans="1:6">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>3</v>
       </c>
@@ -3333,12 +3352,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="1:6">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>51</v>
       </c>
       <c r="B248">
-        <v>0.4285714285714285</v>
+        <v>0.42857142857142849</v>
       </c>
       <c r="C248" t="s">
         <v>1</v>
@@ -3350,12 +3369,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="249" spans="1:6">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>37</v>
       </c>
       <c r="B249">
-        <v>0.2259144708562258</v>
+        <v>0.22591447085622579</v>
       </c>
       <c r="C249" t="s">
         <v>1</v>
@@ -3367,7 +3386,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="251" spans="1:6">
+    <row r="251" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>2</v>
       </c>
@@ -3375,7 +3394,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="252" spans="1:6">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>4</v>
       </c>
@@ -3383,7 +3402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:6">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>5</v>
       </c>
@@ -3391,7 +3410,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="254" spans="1:6">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>6</v>
       </c>
@@ -3399,7 +3418,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="255" spans="1:6">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>7</v>
       </c>
@@ -3407,7 +3426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:6">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>8</v>
       </c>
@@ -3415,7 +3434,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="257" spans="1:6">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>10</v>
       </c>
@@ -3423,12 +3442,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="258" spans="1:6">
+    <row r="258" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="259" spans="1:6">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>13</v>
       </c>
@@ -3448,7 +3467,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="260" spans="1:6">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>55</v>
       </c>
@@ -3465,7 +3484,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="261" spans="1:6">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>3</v>
       </c>
@@ -3482,12 +3501,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="262" spans="1:6">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>52</v>
       </c>
       <c r="B262">
-        <v>0.4285714285714285</v>
+        <v>0.42857142857142849</v>
       </c>
       <c r="C262" t="s">
         <v>1</v>
@@ -3499,12 +3518,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="263" spans="1:6">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>37</v>
       </c>
       <c r="B263">
-        <v>0.2259144708562258</v>
+        <v>0.22591447085622579</v>
       </c>
       <c r="C263" t="s">
         <v>1</v>
@@ -3516,7 +3535,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="265" spans="1:6">
+    <row r="265" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>2</v>
       </c>
@@ -3524,7 +3543,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="266" spans="1:6">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>4</v>
       </c>
@@ -3532,7 +3551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:6">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>5</v>
       </c>
@@ -3540,7 +3559,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="268" spans="1:6">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>6</v>
       </c>
@@ -3548,7 +3567,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="269" spans="1:6">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>7</v>
       </c>
@@ -3556,7 +3575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:6">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>8</v>
       </c>
@@ -3564,7 +3583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="271" spans="1:6">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>10</v>
       </c>
@@ -3572,12 +3591,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="272" spans="1:6">
+    <row r="272" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="273" spans="1:6">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>13</v>
       </c>
@@ -3597,7 +3616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="274" spans="1:6">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>15</v>
       </c>
@@ -3614,7 +3633,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="275" spans="1:6">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>34</v>
       </c>
@@ -3631,7 +3650,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="276" spans="1:6">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>69</v>
       </c>
@@ -3651,4 +3670,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{d465f887-04a9-4c17-8b62-103eddccf68b}" enabled="1" method="Standard" siteId="{ca2a7f76-dbd7-4ec0-9108-6b3d524fb7c8}" removed="0"/>
+</clbl:labelList>
 </file>